--- a/docs/PD_Risk_Register_v1.0.xlsx
+++ b/docs/PD_Risk_Register_v1.0.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="174">
   <si>
     <t>PulseDesk — Risk Register</t>
   </si>
@@ -428,6 +428,90 @@
   </si>
   <si>
     <t>Codebase kept dependency-light and documented so a second developer can pick it up from the Code Register</t>
+  </si>
+  <si>
+    <t>RSK-013</t>
+  </si>
+  <si>
+    <t>A viral share pushes the worker past the free 100,000 requests per day</t>
+  </si>
+  <si>
+    <t>Instagram traffic spike</t>
+  </si>
+  <si>
+    <t>Requests are throttled and the web app stops loading data</t>
+  </si>
+  <si>
+    <t>Edge caching at 60 s to 30 min means users share responses rather than each triggering one; the desktop app calls upstreams directly and is unaffected; raise cache TTLs if the ceiling is approached</t>
+  </si>
+  <si>
+    <t>RSK-014</t>
+  </si>
+  <si>
+    <t>Distribution</t>
+  </si>
+  <si>
+    <t>Unsigned Windows installer triggers a SmartScreen warning and users abandon the download</t>
+  </si>
+  <si>
+    <t>No code-signing certificate</t>
+  </si>
+  <si>
+    <t>Lower install conversion, perception of malware</t>
+  </si>
+  <si>
+    <t>Release notes and the download page explain the warning and the More info to Run anyway path; signing is deferred because it is a recurring paid cost</t>
+  </si>
+  <si>
+    <t>RSK-015</t>
+  </si>
+  <si>
+    <t>Analytics</t>
+  </si>
+  <si>
+    <t>Visitor counts drift when users clear site data or use several devices</t>
+  </si>
+  <si>
+    <t>Deliberate absence of accounts</t>
+  </si>
+  <si>
+    <t>People totals read high, retention reads low</t>
+  </si>
+  <si>
+    <t>Counts are presented as devices rather than people in the dashboard copy; opens per day remains the reliable engagement figure</t>
+  </si>
+  <si>
+    <t>RSK-016</t>
+  </si>
+  <si>
+    <t>Upstream providers throttle Cloudflare datacentre IP ranges, so the web build breaks while the desktop build keeps working</t>
+  </si>
+  <si>
+    <t>Datacentre traffic filtering</t>
+  </si>
+  <si>
+    <t>Mobile and web users see empty panels</t>
+  </si>
+  <si>
+    <t>The /api/health endpoint reports each upstream separately; Stooq fallback covers US tickers; the fallback chain in stocks.js accepts an extra provider without restructuring</t>
+  </si>
+  <si>
+    <t>2026-10-15</t>
+  </si>
+  <si>
+    <t>RSK-017</t>
+  </si>
+  <si>
+    <t>A user assumes the anonymous counter tracks them personally and distrusts the app</t>
+  </si>
+  <si>
+    <t>Any analytics at all</t>
+  </si>
+  <si>
+    <t>Reputational harm, uninstalls</t>
+  </si>
+  <si>
+    <t>The stats page and the retention policy both state plainly that no IP, cookie, email or account is stored; the identifier is client-generated and resettable by clearing site data</t>
   </si>
   <si>
     <t>Metric</t>
@@ -1200,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1789,6 +1873,226 @@
         <v>101</v>
       </c>
     </row>
+    <row r="14" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="F14" s="8">
+        <v>2</v>
+      </c>
+      <c r="G14" s="8">
+        <v>4</v>
+      </c>
+      <c r="H14" s="9">
+        <f>F14*G14</f>
+      </c>
+      <c r="I14" s="9">
+        <f>IF(H14&gt;=15,"High",IF(H14&gt;=8,"Medium","Low"))</f>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="M14" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="N14" s="8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F15" s="3">
+        <v>5</v>
+      </c>
+      <c r="G15" s="3">
+        <v>3</v>
+      </c>
+      <c r="H15" s="10">
+        <f>F15*G15</f>
+      </c>
+      <c r="I15" s="10">
+        <f>IF(H15&gt;=15,"High",IF(H15&gt;=8,"Medium","Low"))</f>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="F16" s="8">
+        <v>5</v>
+      </c>
+      <c r="G16" s="8">
+        <v>1</v>
+      </c>
+      <c r="H16" s="9">
+        <f>F16*G16</f>
+      </c>
+      <c r="I16" s="9">
+        <f>IF(H16&gt;=15,"High",IF(H16&gt;=8,"Medium","Low"))</f>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="M16" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="N16" s="8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="F17" s="3">
+        <v>3</v>
+      </c>
+      <c r="G17" s="3">
+        <v>4</v>
+      </c>
+      <c r="H17" s="10">
+        <f>F17*G17</f>
+      </c>
+      <c r="I17" s="10">
+        <f>IF(H17&gt;=15,"High",IF(H17&gt;=8,"Medium","Low"))</f>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="F18" s="8">
+        <v>3</v>
+      </c>
+      <c r="G18" s="8">
+        <v>2</v>
+      </c>
+      <c r="H18" s="9">
+        <f>F18*G18</f>
+      </c>
+      <c r="I18" s="9">
+        <f>IF(H18&gt;=15,"High",IF(H18&gt;=8,"Medium","Low"))</f>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="M18" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="N18" s="8" t="s">
+        <v>81</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1807,15 +2111,15 @@
   <sheetData>
     <row r="1" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>140</v>
+        <v>168</v>
       </c>
       <c r="B2" s="5">
         <f>COUNTA('Risk Register'!A2:A200)</f>
@@ -1823,7 +2127,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>141</v>
+        <v>169</v>
       </c>
       <c r="B3" s="5">
         <f>COUNTIF('Risk Register'!I2:I200,"High")</f>
@@ -1831,7 +2135,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>142</v>
+        <v>170</v>
       </c>
       <c r="B4" s="5">
         <f>COUNTIF('Risk Register'!I2:I200,"Medium")</f>
@@ -1839,7 +2143,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="B5" s="5">
         <f>COUNTIF('Risk Register'!I2:I200,"Low")</f>
@@ -1863,7 +2167,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="B8" s="5">
         <f>ROUND(AVERAGE('Risk Register'!H2:H200),2)</f>
@@ -1871,7 +2175,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>145</v>
+        <v>173</v>
       </c>
       <c r="B9" s="5">
         <f>MAX('Risk Register'!H2:H200)</f>
